--- a/reports/hours_01-2026.xlsx
+++ b/reports/hours_01-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2812,22 +2812,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12.1.2026</t>
+          <t>13.1.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>אשקלון</t>
+          <t>בראבו</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>תיקונים להסכם שכירות</t>
+          <t>שיחת ועידה פנימית</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2843,22 +2843,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>12.1.2026</t>
+          <t>13.1.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>תיקונים להסכם</t>
+          <t>ישיבה פנימית</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2874,22 +2874,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12.1.2026</t>
+          <t>13.1.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>עקיבא איגר</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>גבעת שמואל</t>
+          <t>שללי</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>טיוטת הסכם שותפות ונספחים</t>
+          <t>פגישה ינושבסקי במשרד ובדיקות לאחר פגישה</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="G80" t="inlineStr"/>
     </row>
@@ -2910,17 +2910,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>רוחמה 24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>בראבו</t>
+          <t>קומת קרקע</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>שיחת ועידה פנימית</t>
+          <t>שיחה קוצאי</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G81" t="inlineStr"/>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>אשקלון</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ישיבה פנימית</t>
+          <t>שיחה עמיאל והכנת נספחים</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr"/>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>עקיבא איגר</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>שללי</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>פגישה ינושבסקי במשרד ובדיקות לאחר פגישה</t>
+          <t>כתב שיפוי להסכם</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G83" t="inlineStr"/>
     </row>
@@ -3003,17 +3003,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>רוחמה 24</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>קומת קרקע</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>שיחה קוצאי</t>
+          <t>שיחות רוית ומסמכים רלוונטיים</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="G84" t="inlineStr"/>
     </row>
@@ -3034,17 +3034,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>אשקלון</t>
+          <t>חלקה 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>שיחה עמיאל והכנת נספחים</t>
+          <t>טיוטת הסכם שימוש</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3053,29 +3053,29 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>13.1.2026</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>אשקלון</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>כתב שיפוי להסכם</t>
+          <t>שיחה עמיאל ותיקונים להסכם</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3084,29 +3084,29 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>13.1.2026</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>אלנבי 115</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>שיחות רוית ומסמכים רלוונטיים</t>
+          <t>שיחת זום נירה ואלה</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3115,29 +3115,29 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>13.1.2026</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>חלקה 3</t>
+          <t>גבעת שמואל</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>טיוטת הסכם שימוש</t>
+          <t>זום יועצי ביטוח</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G88" t="inlineStr"/>
     </row>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>אשקלון</t>
+          <t>מכירת מטמנה</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>שיחה עמיאל ותיקונים להסכם</t>
+          <t>ישיבה במשרד עם הרוכשות</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="G89" t="inlineStr"/>
     </row>
@@ -3189,17 +3189,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>אלנבי 115</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>שיחת זום נירה ואלה</t>
+          <t>מייל לשוקי בתוספת צרופות ושיחה רוית</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="G90" t="inlineStr"/>
     </row>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>אלון קפלן</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>גבעת שמואל</t>
+          <t>חרוזים</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>זום יועצי ביטוח</t>
+          <t>תיקונים לטיוטת הסכם מכר ושיחה אלון</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G91" t="inlineStr"/>
     </row>
@@ -3251,17 +3251,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>מכירת מטמנה</t>
+          <t>הארכת חוזה</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ישיבה במשרד עם הרוכשות</t>
+          <t>מסמכים דרושים לבנק, שיחות פנימיות + הערכות לקלוזינג מול עמרי</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="G92" t="inlineStr"/>
     </row>
@@ -3282,17 +3282,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>יואל רונן</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>ריינס</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>מייל לשוקי בתוספת צרופות ושיחה רוית</t>
+          <t>הסכם מאסטר רוכשים</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G93" t="inlineStr"/>
     </row>
@@ -3313,17 +3313,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>אלון קפלן</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>חרוזים</t>
+          <t>אנרגיה משולבת</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטת הסכם מכר ושיחה אלון</t>
+          <t>טיפול ביפוי כוח להיטל השבחה ושיפוי</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3332,14 +3332,14 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>15.1.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>מסמכים דרושים לבנק, שיחות פנימיות + הערכות לקלוזינג מול עמרי</t>
+          <t>טיפול מול עמרי בקבלת שוברים מפוצלים</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3363,29 +3363,29 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>15.1.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>יואל רונן</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ריינס</t>
+          <t>גבעת שמואל</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>הסכם מאסטר רוכשים</t>
+          <t>עקרונות להסכם שכירות סופר טל</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3401,22 +3401,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>15.1.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>אנרגיה משולבת</t>
+          <t>משאבי שדה</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>טיפול ביפוי כוח להיטל השבחה ושיפוי</t>
+          <t>תצהירי ביטול הסכם הכנה להגשה</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G97" t="inlineStr"/>
     </row>
@@ -3437,17 +3437,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>הארכת חוזה</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>טיפול מול עמרי בקבלת שוברים מפוצלים</t>
+          <t>טיוטת הסכם אופציה להחתמה בעלי קרקע פוטנצאילים</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3456,29 +3456,29 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15.1.2026</t>
+          <t>18.01.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>לנצ'ט</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>גבעת שמואל</t>
+          <t>פינוי בינוי</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>עקרונות להסכם שכירות סופר טל</t>
+          <t>ישיבה במשרדי אקרו</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3487,29 +3487,29 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15.1.2026</t>
+          <t>18.01.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>משאבי שדה</t>
+          <t>חלקה 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>תצהירי ביטול הסכם הכנה להגשה</t>
+          <t>כתב שיפוי והסכם שימוש</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3518,29 +3518,29 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15.1.2026</t>
+          <t>18.01.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>צידוניה</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>טיוטת הסכם אופציה להחתמה בעלי קרקע פוטנצאילים</t>
+          <t>הסכם דוראל</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3549,40 +3549,3326 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>שמשון זליג</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>הארכת תקופת בנייה</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>פרוטוקול וייפוי כוח</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>אושירה</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>בראבו</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם שכירות</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>מתחם השעון</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>העברת מסמכים דוקטור שקשוקה</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>יואל רונן</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>המעיין 7</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>עיקרי טיעון לערר</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>אגרוטופ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>תימורים</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>מכתב לרמי ירושלים לקראת פגישה</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>נחשון</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>פנייה לרמי</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ירדן חובב</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>רכישת דירה</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>בדיקת תיק בניין</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>שמעון הצדיק</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>רישום זכויות בטאבו</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>כפיר דהן</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>קצרין</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>רישום הערת אזהרה</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>אלון קפלן</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>אנה פרנק 23</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>טיפול בשומות</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>אודי שגב</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>היטלים</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ריכוז עיקרי טיעון</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>18.01.2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>אקרשטיין</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>רישום זכויות</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>השלמת מסמכים</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>19.1.2026</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>דלק</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>משאבי שדה</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>שליחות למסמ"ק</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>הוצאות</t>
         </is>
       </c>
-      <c r="F102" t="n">
+      <c r="F114" t="n">
         <v>120</v>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>אגרוטופ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>תימורים</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ישיבה ברמי ירושלים</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>מפעלי נשק</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>מגרש 52</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>פגישה ברמי ירושלים</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>נחשון</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>פגישה ברמי ירושלים</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>מבוא ביתר</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>פגישה ברמי ירושלים</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>משאבי שדה</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>טיפול בביטול עסקה</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>דלק נכסים</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>גל חברה לדלק</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>טיפול בקבלת החזר מס רכוש</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>יואל רונן</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>המעיין 7</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>הכנה לדיון בערעור מנהלי</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>שמשון זליג</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>הארכת תקופת בנייה</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>בדיקת תיק רמי</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>גבעוני</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>הארכת חוזה</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>מכתב לרמי לצורך קבלת חשבוניות והמצאת ערבות</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>19.01.2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>עתירה מנהלית</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>בדיקת קלסרים בזן</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>יואל רונן</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>המעיין 7</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>דיון בערעור מנהלי</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>בית בלב</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ישיבת זום</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>רונן כהן</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>מיכאלאנג'לו</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ישיבה עורך דין לולה וצבי והכנה לישיבה</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>אושירה</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>בראבו</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>תיקון נספח א'</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>תיקון להסכם אופציה</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>מנורה</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>גבעת שמואל</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>טיפול בהסכם שכירות הסל שלנו</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>הסכם מאסטר אופציה להסכם שכירות</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ינושבסקי</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>אבן גבירול</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>בקשה לתיקון שיעבוד</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>אודי שגב</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>היטלים</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>שיחה דניאל מסלה</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>g סיטי</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>שיחת גבי והעברת הסכמים</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>יעל רוטשילד</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>מבשרת ציון</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>שוטף</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>עתירה מנהלית</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>מסמכים לגיא לצורך בדיקות</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>משאבי שדה</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>תיקונים למכתב נלווה</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>תחנת סורק</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ישיבה בדלק</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם שכירות</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>רוחמה 24</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>קוצאי</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם פשרה</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>גבעוני</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>הארכת חכירה</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>תשובה להשגה משפטית</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>רמת רחל</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>טיפול במסמכי פתיחת חברה</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>יזרעאל</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>עדכון נספח ד</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>נייר חדרה</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>חלקה 8</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>תיקונים לכתב שיפוי</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ש.ב.ה</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>הסכמי מכירה</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>שיחה אמיר</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ריכוז תנאים מסחריים מהסכמים ותיקון הסכמים</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>חניתה</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>התייחסות לטיוטה</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>כפיר דהן</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>מכירה כדורי</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>מסמכים לבא כוח קונה ושיחה</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>משאבי שדה</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>טיפול בביטול הסכם</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>עקיבא איגר</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>רוכשים</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>רישום הערות אזהרה</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>שמשון זליג</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>הארכת תקופת בנייה</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>הזמנת מסמכים מהטאבו</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>יואל רונן</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ריינס 30</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>עריכת טיוטת הסכם מאסטר</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>רוחמה 24</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>קוצאי</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם פשרה ושיחה קוצאי</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>חיימסון</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>רישום בית משותף</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>בדיקת תיק בניין</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>שמשון זליג</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>בקשה להקניית בעלות</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>הכנת מסמכים</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>נייר חדרה</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>חלקה 26</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>התכתבות סיגלית</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ירדן חובב</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>רכישת דירה</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>הערות להסכם מכר</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>קן דרור</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>חוף התכלת</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>מסמכים לפריסת מס שבח</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>רוחמה 24</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>קוצאי</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>תיקונים להסכם פשרה</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>אשקלון</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>תיקונים להסכם שכירות</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>עין כרמל</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>תיקונים להסכם</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>מנורה</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>גבעת שמואל</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם שותפות ונספחים</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>נייר חדרה</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>חלקה 26</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>התכתבות סיגלית</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ירדן חובב</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>רכישת דירה</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>הערות להסכם מכר</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>קן דרור</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>חוף התכלת</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>מסמכים לפריסת מס שבח</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>24.1.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>רוחמה 24</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>קוצאי</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>תיקונים להסכם פשרה</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>g סיטי</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>פגישה במשרדי g סיטי</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>פגישה דוראל במשרד</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>אגירה ביצוע</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>תקנות שותפות</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>שמשון זליג</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>בקשה להקניית בעלות</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>מסמכים להקניית בעלות והפצה</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ש.ב.א</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>תביעה רמי</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>שיחה אברבוך</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>קן דרור</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>חוף התכלת</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>מסמכים למיסוי מקרקעין</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>בוחבוט</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>מעלות</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>מסמכים לתיקון שטח חוזה</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>27.01.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>מפעלי נשק</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>קריית גת</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>דיון בהשגה ברמי ירושלים והכנה</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>4</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>27.01.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>הסכם דוראל טיפול שוטף</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>צליל החורש</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>סיור בצליל החורש</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>4</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>יעל רוטשילד</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>מבשרת ציון</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>שיחה ענת ויעל</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>אודי שגב</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>היטלים</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>פגישה במשרד עורכי דין עירייה והכנה</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>מיכל רוזנבלט</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>העברת נכסים</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>פגישה במשרד</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>עודד מרגלית</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>בית הטקסטיל</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>בדיקת מסמכים שהתקבלו מבא כוח מוכר</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>עקיבא איגר</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>הסכם שכירות דירה 41</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם ותיקונים</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>גודלן קייר</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>טיפול בהקמת שותפות</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>תיקון טיוטות</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>רמלה</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>טיפול בקבלת אישורים לרישום</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>נייר חדרה</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>חלקה 26</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>מכתב לרמי חידוש חכירה</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>28.01.2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>כפיר דהן</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>מכירה כדורי</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם מכר תיקונים</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>פיצול נכסים</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ישיבה פנימית בעניין פיצול נכסים + פגישת זום פליקס ויהל</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ש.ב.ה</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>רכישת מניות</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>שיחת זום עם הצדדים</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>רוחמה 24</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>קוצאי</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>תיקון טיוטת הסכם פשרה</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>כפיר דהן</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>מכירה כדורי</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם מכר תיקונים</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>עין כרמל</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>טיוטת הסכם שהתקבלה</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>יעל רוטשילד</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>מבשרת ציון</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>התייחסות להסכם בין יעל לקליגמן</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>עין יהב</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>חידוש חוזה חכירה התכתבות סוניה</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>נספחים להסכם שכירות</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>עודד מרגלית</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>בית הטקסטיל</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ריכוז בדיקות</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>עודד מרגלית</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>בית הטקסטיל</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>+בדיקת תיק ניהול ובדיקת תיק חניון</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>נייר חדרה</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>חלקה 8</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>תיקונים לכתב שיפוי ושיחה אילן</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>מפעלי נשק</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>קריית גת</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>טיפול בקבלת חוזה חכירה</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>גבעוני</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>הארכת חוזה</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>תגובה לתשובה להשגה משפטית</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>עתירה מנהלית</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>שיחות פנימיות והתכתבות ספי</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>יעל רוטשילד</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>מבשרת ציון</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>שוטף</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>צידוניה</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>נספחים להסכם דוראל</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>שמשון זליג</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>הארכת תקופת בנייה</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>בדיקת תסריט חלוקה</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>קן דרור</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>חוף התכלת</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>טיפול במיסים</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>30.1.2026</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>גבעוני</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>הארכת חכירה</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>תשובה למענה להשגה גבעוני</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>31.01.2026</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>גבעוני</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>חוות דעת לענין דמי שימוש</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>טיוטת חוות דעת</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>31.01.2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>יעל רוטשילד</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>מבשרת ציון</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>התייחסות להערות יעל להסכם עם קליגמן</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>31.01.2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>אגירה</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>חצי חינם שרונים</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>טיוטת חוות דעת לבנק לאומי</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
